--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_AnhTuanNB(NamAnh)_270726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/02. Trả bảo hành/TBH_AnhTuanNB(NamAnh)_270726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E24CF0-83D4-4BF2-A874-4CE9BE0C61EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C902E43-39EF-431E-8AA7-8565C4569988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,9 +123,6 @@
     <t>Cấu hình test lại thiết bị</t>
   </si>
   <si>
-    <t>Thương xuyên mất GPS</t>
-  </si>
-  <si>
     <t>0032004E1E</t>
   </si>
   <si>
@@ -141,6 +138,9 @@
   <si>
     <t>Tách led hồng ngoại lỗi, 
 thay module GPS</t>
+  </si>
+  <si>
+    <t>Lỗi led hồng ngoại, thường xuyên mất GPS</t>
   </si>
 </sst>
 </file>
@@ -539,6 +539,45 @@
     <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -562,45 +601,6 @@
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -992,48 +992,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40" t="s">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41" t="s">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="44" t="s">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="46"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="59"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="60" t="s">
         <v>9</v>
       </c>
@@ -1044,25 +1044,25 @@
       <c r="I4" s="62"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="26"/>
       <c r="F6" s="27"/>
       <c r="G6" s="27"/>
@@ -1072,12 +1072,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="26"/>
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
@@ -1085,12 +1085,12 @@
       <c r="I7" s="28"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="26"/>
       <c r="F8" s="27"/>
       <c r="G8" s="27"/>
@@ -1098,12 +1098,12 @@
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="26"/>
       <c r="F9" s="27"/>
       <c r="G9" s="27"/>
@@ -1141,73 +1141,73 @@
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="24" x14ac:dyDescent="0.25">
-      <c r="A11" s="55">
+      <c r="A11" s="39">
         <v>1</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56" t="s">
+      <c r="F11" s="40"/>
+      <c r="G11" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="56" t="s">
+      <c r="H11" s="40" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="25"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55">
+      <c r="A12" s="39">
         <v>2</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56" t="s">
+      <c r="D12" s="40"/>
+      <c r="E12" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56" t="s">
+      <c r="F12" s="40"/>
+      <c r="G12" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="56" t="s">
+      <c r="H12" s="40" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="25"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55">
+      <c r="A13" s="39">
         <v>3</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56" t="s">
+      <c r="C13" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="56" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="40" t="s">
         <v>37</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>36</v>
       </c>
       <c r="I13" s="25">
         <v>260000</v>
@@ -1215,40 +1215,40 @@
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55">
+      <c r="A14" s="39">
         <v>4</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56" t="s">
+      <c r="C14" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56" t="s">
+      <c r="F14" s="40"/>
+      <c r="G14" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="56" t="s">
-        <v>35</v>
+      <c r="H14" s="40" t="s">
+        <v>34</v>
       </c>
       <c r="I14" s="25"/>
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="59"/>
+      <c r="A15" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="38">
         <f>SUM(I11:I14)</f>
         <v>260000</v>
@@ -1279,34 +1279,34 @@
       <c r="I17" s="20"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
       <c r="E18" s="30"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="32"/>
       <c r="F19" s="33"/>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="22"/>
@@ -1353,19 +1353,19 @@
       <c r="I23" s="16"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35"/>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
@@ -1379,12 +1379,17 @@
       <c r="I25" s="18"/>
     </row>
     <row r="27" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
     </row>
     <row r="66" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A6:D6"/>
@@ -1398,11 +1403,6 @@
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="99" orientation="landscape" r:id="rId1"/>
